--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES I-X/FRACC II/LTAIPT_A63F02A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES I-X/FRACC II/LTAIPT_A63F02A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="342">
   <si>
     <t>48947</t>
   </si>
@@ -115,7 +115,7 @@
     <t>Denominación del área</t>
   </si>
   <si>
-    <t>Denominación del puesto</t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Denominación del cargo (de conformidad con nombramiento otorgado)</t>
@@ -127,10 +127,10 @@
     <t>Denominación de la norma que establece atribuciones, responsabilidades y/o funciones y el fundamento legal (artículo y/o fracción)</t>
   </si>
   <si>
-    <t>Atribuciones, responsabilidades y/o funciones, según sea el caso</t>
-  </si>
-  <si>
-    <t>Hipervínculo al perfil y/o requerimientos del puesto o cargo, en su caso</t>
+    <t>Atribuciones, responsabilidades y/o funciones, según sea el caso (Redactadas con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Hipervínculo al perfil y/o requerimientos del puesto o cargo, en su caso (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Número total de prestadores de servicios profesionales</t>
@@ -148,22 +148,292 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Departamento de Formación y Desarrollo Docente</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Formación y Desarrollo Docente</t>
+  </si>
+  <si>
+    <t>Subdirección de Seguimiento Académico</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Artículo 23</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>Departamento de Bibliotecas y Laboratorio</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Bibliotecas y Laboratorio</t>
+  </si>
+  <si>
+    <t>Artículo 24</t>
+  </si>
+  <si>
+    <t>Jefatura de Materia</t>
+  </si>
+  <si>
+    <t>Jefe de materia</t>
+  </si>
+  <si>
+    <t>Artículo 25</t>
+  </si>
+  <si>
+    <t>Departamento de Planes y Programas de Estudio</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Planes y Programas de Estudio</t>
+  </si>
+  <si>
+    <t>Artículo 22</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Director del Plantel</t>
+  </si>
+  <si>
+    <t>Director del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona II/ Dirección General</t>
+  </si>
+  <si>
+    <t>Artículo 47</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 05 Panzacola</t>
   </si>
   <si>
     <t>Subdirector del Plantel</t>
   </si>
   <si>
+    <t>Subdirector Académico del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Ver nota</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>Subdirector de Área</t>
+  </si>
+  <si>
+    <t>Subdirector de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>Artículo 26</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 09 Tlaxco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Director del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona III/ Dirección General</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativa del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona IV/ Dirección General</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 20 Ixtenco.</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 24 Tizatlán</t>
+  </si>
+  <si>
+    <t>Director del Plantel 24 Tizatlán</t>
+  </si>
+  <si>
+    <t>Subdirección del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Director de Plante 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Subdirección del Plantel 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 23 San Pablo</t>
+  </si>
+  <si>
+    <t>Director del Plantel 23 San Pablo</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona III</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial Zona III</t>
+  </si>
+  <si>
+    <t>Dirección General</t>
+  </si>
+  <si>
+    <t>Artículo 40</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Administrativos</t>
+  </si>
+  <si>
+    <t>Artículo 33</t>
+  </si>
+  <si>
+    <t>Departamento de Inventarios</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Inventarios</t>
+  </si>
+  <si>
+    <t>Artículo 35</t>
+  </si>
+  <si>
+    <t>Subdirector de Servicios Administrativos</t>
+  </si>
+  <si>
+    <t>Dirección Administrativa</t>
+  </si>
+  <si>
+    <t>Artículo 32</t>
+  </si>
+  <si>
+    <t>Departamento de Recursos Materiales y Servicios Generales</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Recursos Materiales y Servicios Generales</t>
+  </si>
+  <si>
+    <t>Artículo 34</t>
+  </si>
+  <si>
+    <t>Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>Subdirector Financiero</t>
+  </si>
+  <si>
+    <t>Artículo 36</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>Artículo 37</t>
+  </si>
+  <si>
+    <t>Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>Artículo 38</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona I</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial Zona I</t>
+  </si>
+  <si>
     <t>Dirección del Plantel 01 Tlaxcala</t>
   </si>
   <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Departamento de Recursos Humanos</t>
+    <t>Director del Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona I/ Dirección General</t>
   </si>
   <si>
     <t>Subdirección Administrativo del Plantel 01 Tlaxcala</t>
@@ -172,259 +442,232 @@
     <t>Subdirector Administrativo del Plantel 01 Tlaxcala</t>
   </si>
   <si>
-    <t>Director del Plantel</t>
-  </si>
-  <si>
-    <t>Director del Plantel 01 Tlaxcala</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona I/ Dirección General</t>
-  </si>
-  <si>
-    <t>Artículo 47</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona I</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona I</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>Artículo 40</t>
-  </si>
-  <si>
-    <t>Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>Subdirección Financiera</t>
-  </si>
-  <si>
-    <t>Artículo 38</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>Artículo 37</t>
-  </si>
-  <si>
-    <t>Subdirector de Área</t>
-  </si>
-  <si>
-    <t>Subdirector Financiero</t>
-  </si>
-  <si>
-    <t>Dirección Administrativa</t>
-  </si>
-  <si>
-    <t>Artículo 36</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 24 Tizatlán</t>
-  </si>
-  <si>
-    <t>Director del Plantel 24 Tizatlán</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona IV/ Dirección General</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 20 Ixtenco.</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>Artículo 35</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Recursos Humanos</t>
-  </si>
-  <si>
-    <t>Artículo 33</t>
-  </si>
-  <si>
-    <t>Subdirector de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>Artículo 32</t>
+    <t>Subdirección Académica del Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Director del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativo del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 04 Chuiautempan</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 21 Ayometla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 21 Ayometla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 22 Texoloc</t>
+  </si>
+  <si>
+    <t>Director del Plantel 22 Texoloc</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona II</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial Zona II</t>
+  </si>
+  <si>
+    <t>Director del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Director del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Director del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 07 Buenavista</t>
+  </si>
+  <si>
+    <t>Director del Plantel 07 Buenavista</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 09 Tlaxco</t>
+  </si>
+  <si>
+    <t>Director del Plantel 09 Tlaxco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 12 Santa Cruz</t>
+  </si>
+  <si>
+    <t>Director del Plantel 12 Santa Cruz</t>
+  </si>
+  <si>
+    <t>Subdirección Plantel 12 Santa Cruz</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Director del Plantel 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona IV</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial Zona IV</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Director del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 18 Atltzayanca</t>
+  </si>
+  <si>
+    <t>Director del Plantel 18 Altzayanca</t>
+  </si>
+  <si>
+    <t>Dirección de  Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Director del Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Subdirección de actividades paraescolares</t>
+  </si>
+  <si>
+    <t>Artículo 29</t>
+  </si>
+  <si>
+    <t>Departamento de actividades deportivas</t>
+  </si>
+  <si>
+    <t>Jefe  de Departamento de actividades deportivas</t>
+  </si>
+  <si>
+    <t>Subdirección de paraescolares</t>
+  </si>
+  <si>
+    <t>Artículo 31</t>
+  </si>
+  <si>
+    <t>Departamento de Control Escolar</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Control Escolar</t>
+  </si>
+  <si>
+    <t>Artículo 27</t>
   </si>
   <si>
     <t>Director Administrativo</t>
   </si>
   <si>
-    <t>Artículo 31</t>
-  </si>
-  <si>
-    <t>Dirección de  Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Director del Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>Director del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>Departamento de actividades deportivas</t>
-  </si>
-  <si>
-    <t>Jefe  de Departamento de actividades deportivas</t>
-  </si>
-  <si>
-    <t>Subdirección de paraescolares</t>
-  </si>
-  <si>
-    <t>Subdirección de actividades paraescolares</t>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>Artículo 29</t>
-  </si>
-  <si>
-    <t>Departamento de Control Escolar</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Control Escolar</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Escolares</t>
-  </si>
-  <si>
-    <t>Artículo 27</t>
-  </si>
-  <si>
-    <t>Subdirector de Servicios Escolares</t>
-  </si>
-  <si>
-    <t>Artículo 26</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 18 Atltzayanca</t>
-  </si>
-  <si>
-    <t>Director del Plantel 18 Altzayanca</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 17 Cuapiaxtla</t>
-  </si>
-  <si>
-    <t>Director del Plantel 17 Cuapiaxtla</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Departamento de Planes y Programas de Estudio</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Planes y Programas de Estudio</t>
-  </si>
-  <si>
-    <t>Subdirección de Seguimiento Académico</t>
-  </si>
-  <si>
-    <t>Artículo 22</t>
-  </si>
-  <si>
-    <t>Departamento de Bibliotecas y Laboratorio</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Bibliotecas y Laboratorio</t>
-  </si>
-  <si>
-    <t>Artículo 24</t>
-  </si>
-  <si>
-    <t>Departamento de Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>Artículo 23</t>
-  </si>
-  <si>
-    <t>Jefatura de Materia</t>
-  </si>
-  <si>
-    <t>Jefe de materia</t>
-  </si>
-  <si>
-    <t>Artículo 25</t>
-  </si>
-  <si>
-    <t>Director del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona IV</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona IV</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 15 Hueyotlipan</t>
-  </si>
-  <si>
-    <t>Director del Plantel 15 Hueyotlipan</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona III/ Dirección General</t>
-  </si>
-  <si>
-    <t>Subdirección Plantel 12 Santa Cruz</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 12 Santa Cruz</t>
+    <t>Director de Area</t>
+  </si>
+  <si>
+    <t>Secretario General del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel B</t>
+  </si>
+  <si>
+    <t>Subdirector de Plantel B</t>
+  </si>
+  <si>
+    <t>Unidad de Control Interno</t>
+  </si>
+  <si>
+    <t>Contralor Interno</t>
+  </si>
+  <si>
+    <t>Contralor Interno del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Artículo 52</t>
+  </si>
+  <si>
+    <t>Departamento de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>Artículo 18</t>
+  </si>
+  <si>
+    <t>Directora Académica</t>
   </si>
   <si>
     <t>Subdirector de Seguimiento Académico</t>
@@ -433,13 +676,28 @@
     <t>Artículo 21</t>
   </si>
   <si>
-    <t>Departamento de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>Artículo 18</t>
+    <t>Departamento de Información y Relaciones Públicas</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Información y Relaciones Públicas</t>
+  </si>
+  <si>
+    <t>Artículo 19</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>Subdirector Jurídico</t>
+  </si>
+  <si>
+    <t>Artículo 15</t>
+  </si>
+  <si>
+    <t>Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>Artículo 16</t>
   </si>
   <si>
     <t>Subdirección de Planeación y Evaluación Institucional</t>
@@ -451,85 +709,127 @@
     <t>Artículo 17</t>
   </si>
   <si>
-    <t>Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>Artículo 16</t>
-  </si>
-  <si>
-    <t>Director del Plantel 12 Santa Cruz</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Director del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Subdirector Jurídico</t>
-  </si>
-  <si>
-    <t>Artículo 15</t>
-  </si>
-  <si>
-    <t>Departamento de Información y Relaciones Públicas</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Información y Relaciones Públicas</t>
-  </si>
-  <si>
-    <t>Artículo 19</t>
-  </si>
-  <si>
-    <t>Unidad de Control Interno</t>
-  </si>
-  <si>
-    <t>Contralor Interno</t>
-  </si>
-  <si>
-    <t>Contralor Interno del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Artículo 52</t>
-  </si>
-  <si>
-    <t>Secretaría General</t>
-  </si>
-  <si>
-    <t>Secretario General del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 09 Tlaxco</t>
-  </si>
-  <si>
-    <t>Director del Plantel 09 Tlaxco</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 07 Buenavista</t>
-  </si>
-  <si>
-    <t>Director del Plantel 07 Buenavista</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 03 Calpulalpan</t>
+    <t>Director General</t>
+  </si>
+  <si>
+    <t>Director General del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Junta Directiva - Gobierno del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Artículo 10</t>
+  </si>
+  <si>
+    <t>E64482F6E475B31BC261BB8FF5173EC2</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>14/07/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril de 2023 al 30 de junio de 2023, en el Colegio de Bachilleres del Estado de Tlaxcala, de acuerdo a la norma que establece atribuciones responsabilidades y/o funciones, estos son nombrados y se rigen de acuerdo los articulos 16, 18 y 30 de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala y al articulo 21 fraccion VIII del Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala.  El Director como autortidad superior jerarquica de Plantel, tiene la facultad de asignar las funciones a realizar a los subdirectores, con relación a los prestadores de servicios profesionales que formen parte de la estructura orgánica, este sujeto obligado no genero información respecto a este tema.</t>
+  </si>
+  <si>
+    <t>D77E6AE3A2BAB7D32EFFCF8A1A29DEB0</t>
+  </si>
+  <si>
+    <t>88899D8254217A9A67DA5390225F72C3</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril de 2023 al 30 de junio de 2023, en el Colegio de Bachilleres del Estado de Tlaxcala, es facultad del Director General  proponer ante la Junta Directiva las candidaturas para ocupar las Direcciones de las unidades administrativas y de los planteles, motivo por el cual no se tiene ninguna norma establecida con los requerimientos del puesto  para cubrir  un perfil Directivo. De igual forma este Colegio de Bachilleres del Estado de Tlaxcala, no cuenta con prestadores de servicios profesionales que formen parte de la estructura orgánica, por lo tanto no hay información que reportar.</t>
+  </si>
+  <si>
+    <t>A8502E41931326AD599C7C003DA63AE1</t>
+  </si>
+  <si>
+    <t>Subdirectora del Plantel</t>
+  </si>
+  <si>
+    <t>4E09EFE78D807B6705A8DE45C747EBF8</t>
+  </si>
+  <si>
+    <t>Coordinadora Sectorial</t>
+  </si>
+  <si>
+    <t>FF8C8D1B01425D58A342AE51AA4639F4</t>
+  </si>
+  <si>
+    <t>D9F46145E3AC22726801113568D3E5EB</t>
+  </si>
+  <si>
+    <t>Directora del Plantel</t>
+  </si>
+  <si>
+    <t>C781326412FEC91936E7012B0687ED1E</t>
+  </si>
+  <si>
+    <t>C5DB4D40A92A7AE8A0E2D673CDC59389</t>
+  </si>
+  <si>
+    <t>35EBBE94F2DB1378DC7201ECDE41A81F</t>
+  </si>
+  <si>
+    <t>402928129BE9AFAF6515A201EC37B1C5</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>40D3BC1290962A412E3B079A4AA5EA5B</t>
+  </si>
+  <si>
+    <t>C269A9C723AFCC9D8A5F8DCBAC14BE40</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>CD4F2BF69B60371C77E922119E4FF4F5</t>
+  </si>
+  <si>
+    <t>7E8575226E65ED56D42B5FDBDB793790</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 13 Papalotla</t>
+  </si>
+  <si>
+    <t>5D41F436004ECBD25661F18911620E64</t>
+  </si>
+  <si>
+    <t>3D14C1381140C0161B58BFC47D154C3B</t>
+  </si>
+  <si>
+    <t>5A62D7E7E67CFE171BD40F0B66CFE11B</t>
+  </si>
+  <si>
+    <t>D3229BC8261AFA9125BC9F5135D69F3F</t>
+  </si>
+  <si>
+    <t>94EC0AC766C47945F9EF6F7139244B23</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>D10060F25A45AFCC93B3EBBD36856199</t>
+  </si>
+  <si>
+    <t>4D8A1EB23228F146ED62165D5C3770F4</t>
+  </si>
+  <si>
+    <t>09CE3599AD497608B9D596B54BD47481</t>
+  </si>
+  <si>
+    <t>49873E65CBA2B48094B1838EE73D304A</t>
+  </si>
+  <si>
+    <t>335B049CB7B6B2DC92628B9A6153A342</t>
   </si>
   <si>
     <t>Subdirección Administrativa del Plantel 03 Calpulalpan</t>
@@ -538,418 +838,208 @@
     <t>Subdirector Administrativo del Plantel 03 Calpulalpan</t>
   </si>
   <si>
-    <t>Director General</t>
-  </si>
-  <si>
-    <t>Director General del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Junta Directiva - Gobierno del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Artículo 10</t>
-  </si>
-  <si>
-    <t>Director del Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona III</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona III</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 23 San Pablo</t>
-  </si>
-  <si>
-    <t>Director del Plantel 23 San Pablo</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona II/ Dirección General</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>Director del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Director del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Subdirección del Plantel 13 Papalotla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 13 Papalotla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 13 Papalotla</t>
-  </si>
-  <si>
-    <t>Director de Plante 13 Papalotla</t>
-  </si>
-  <si>
-    <t>Subdirección del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Director del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>Director del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona II</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona II</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 22 Texoloc</t>
-  </si>
-  <si>
-    <t>Director del Plantel 22 Texoloc</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Director del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativo del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 04 Chuiautempan</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>Director del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>B1220CA973AAC30A171B4F1E601A5D91</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>14/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de julio de 2022 al 30 de septiembre de 2022, en el Colegio de Bachilleres del Estado de Tlaxcala, es facultad del Director General  proponer ante la Junta Directiva las candidaturas para ocupar las Direcciones de las unidades administrativas y de los planteles, motivo por el cual no se tiene ninguna norma establecida con los requerimientos del Puesto  para cubrir  un perfil Directivo. De igual forma este Colegio de Bachilleres del Estado de Tlaxcala, no cuenta con prestadores de servicios profesionales que formen parte de la estructura orgánica, por lo tanto no hay información que reportar.</t>
-  </si>
-  <si>
-    <t>612333DE34BE562CED9C5BD47B383152</t>
-  </si>
-  <si>
-    <t>8476FFCACB545FE5F6EE7D76CFD5254E</t>
-  </si>
-  <si>
-    <t>41029DFA16A046FF35444497E289C50F</t>
-  </si>
-  <si>
-    <t>B425A997DBB59B92CE92C10F304B0938</t>
-  </si>
-  <si>
-    <t>BBA5BB725FDC30B8A676D0C07E81A469</t>
-  </si>
-  <si>
-    <t>23341895DBB4B07EE4E0A2E59AB307CD</t>
-  </si>
-  <si>
-    <t>2BB80D7EAED68262C6889EAB21C128CD</t>
-  </si>
-  <si>
-    <t>C63024E5CD7C938B48B6A730BFC2C445</t>
-  </si>
-  <si>
-    <t>D68764EF37A5406FD46A8E91021C95A9</t>
-  </si>
-  <si>
-    <t>8187C3C861F401FC14FDF0DE1DFED251</t>
-  </si>
-  <si>
-    <t>520CDCD6CF38D20261CE2067896BBBB7</t>
-  </si>
-  <si>
-    <t>11C8A884C7A4E9EF1B66E37E169A4D8F</t>
-  </si>
-  <si>
-    <t>882758BFDB95129A421A4EEBC4F2CCF0</t>
-  </si>
-  <si>
-    <t>B0B8926B9D4FCD385497707BBC8F060B</t>
-  </si>
-  <si>
-    <t>4982585C90497E2EE45286ADEE117F16</t>
-  </si>
-  <si>
-    <t>CAA3437FDDB1A7C8A61C2A5F2A804F83</t>
-  </si>
-  <si>
-    <t>B0D0AE844B05C2DD95DB393ECB612FB2</t>
-  </si>
-  <si>
-    <t>147ECE2F49A62B151AB679785A94D3BF</t>
-  </si>
-  <si>
-    <t>Director del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>090997C874F8250A92789ED23982FBBA</t>
-  </si>
-  <si>
-    <t>D0E20BB2576D2320476D6272F4BD2097</t>
-  </si>
-  <si>
-    <t>EF0620AF3FC868805FFD87EB8D71580A</t>
-  </si>
-  <si>
-    <t>FBE518C470FDA8D1F035CFE1321DAF59</t>
-  </si>
-  <si>
-    <t>0D3EC9D18C6DD661A6CC7039100EF464</t>
-  </si>
-  <si>
-    <t>01DE71476D7700DF5EE4608FB86FC625</t>
-  </si>
-  <si>
-    <t>7D5DCD3FD8DB33F6084F1C117A1950D9</t>
-  </si>
-  <si>
-    <t>84796DA5F9CA77033CA2AFE01C739F20</t>
-  </si>
-  <si>
-    <t>Departamento de Orientación Educativa</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Orientación Educativa</t>
-  </si>
-  <si>
-    <t>Artículo 28</t>
-  </si>
-  <si>
-    <t>5ABC623FA4E3A4C2D45EBAA4232F842D</t>
-  </si>
-  <si>
-    <t>9C94A15F70D9A5BDBC5ADC6717173BAE</t>
-  </si>
-  <si>
-    <t>6A278EFAFC3D035A25EB82DD5FE57207</t>
-  </si>
-  <si>
-    <t>9AC16EAEC400F68E2CCB85158B9C4B6F</t>
-  </si>
-  <si>
-    <t>F5718E9EFCCB2A3A4DCF19AE21C5F96D</t>
-  </si>
-  <si>
-    <t>EFE221484C64EEE86F8AC6AC3717382B</t>
-  </si>
-  <si>
-    <t>F3B99959BB475C1E1ACDFC7ADF1CD751</t>
-  </si>
-  <si>
-    <t>9E1275765BBE27A4D2A3FB0DE18B070A</t>
-  </si>
-  <si>
-    <t>1D1BB766191308A3C7CF8E5E9470D885</t>
-  </si>
-  <si>
-    <t>056256E07A483D14CD73D611D8C165B9</t>
-  </si>
-  <si>
-    <t>55255A61A5DCBDBC72A20EE3E82DF4DD</t>
-  </si>
-  <si>
-    <t>7C8B3833E9AA0161DA9903C7B2D0BF08</t>
-  </si>
-  <si>
-    <t>9F9A206731679815BF4976EDC84E34E6</t>
-  </si>
-  <si>
-    <t>F8A292E4B427CEECD928126706029D98</t>
-  </si>
-  <si>
-    <t>36597A8AF9ABC959291C354D0E9D627E</t>
-  </si>
-  <si>
-    <t>EBC3FE236214CCA4B6A17ED20C84C254</t>
-  </si>
-  <si>
-    <t>3CA255428581DFC1C6082B90F6A7CE60</t>
-  </si>
-  <si>
-    <t>67688AB0EB79457969FFD36B670F483E</t>
-  </si>
-  <si>
-    <t>4DBA28EA6B07AEA9BB48055861B85BA9</t>
-  </si>
-  <si>
-    <t>1CF97DCA8E57095155172055DC786BA2</t>
-  </si>
-  <si>
-    <t>B1F06655B1D1C3FDFBE32E817B967884</t>
-  </si>
-  <si>
-    <t>12109255BB825350979BBA09A330F135</t>
-  </si>
-  <si>
-    <t>937716D82CC23C2C3CDBD7404EF9B201</t>
-  </si>
-  <si>
-    <t>768D1A653398B3E457D1F61EAEEA7B7B</t>
-  </si>
-  <si>
-    <t>8656C0F1BB1FB034C0AF805A63183A5D</t>
-  </si>
-  <si>
-    <t>CDB51EE1B9D6E35BC42CE17E8A3DBC71</t>
-  </si>
-  <si>
-    <t>4912F8114BDA1228CE383E6335F6D47F</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>383F130D7BAC99B5EDD0F95AAE8E7100</t>
-  </si>
-  <si>
-    <t>5B7F4E284AEB13FD3FB4BD557C96B4C1</t>
-  </si>
-  <si>
-    <t>452794486C5C2CA016BE0DD0413FE4BC</t>
-  </si>
-  <si>
-    <t>ECBD361D8E0FEFB65D9DC1659D810D22</t>
-  </si>
-  <si>
-    <t>64E7C277146C928A0CEF4DB015441677</t>
-  </si>
-  <si>
-    <t>6CEBF301DD5E71B6F8A093079CBF87E3</t>
-  </si>
-  <si>
-    <t>72B487770E3F4D69F517628AF38A4C6C</t>
-  </si>
-  <si>
-    <t>6B569F93CE016F85F6575A1A9C489A30</t>
-  </si>
-  <si>
-    <t>8F3B4332D71EAFC182A64E6B9DEE3360</t>
-  </si>
-  <si>
-    <t>05CBDB7FA9DB97DCA93C2AC186F3C970</t>
-  </si>
-  <si>
-    <t>3279B1EDE926E963B4827A6A21473964</t>
-  </si>
-  <si>
-    <t>083AF7D970D53345A1F832BD32E2856E</t>
-  </si>
-  <si>
-    <t>5776A570DD009F26B55B09B0332BB9B8</t>
-  </si>
-  <si>
-    <t>B472BFA57A371FF83B36FF86A5E72079</t>
-  </si>
-  <si>
-    <t>6CF98EB0D38A2D09F4381395F0993FD7</t>
-  </si>
-  <si>
-    <t>FEDF39291D63A103481CE36EDABBB2B4</t>
-  </si>
-  <si>
-    <t>A05CECC321131FBE70B7E7C8A1F59DEA</t>
-  </si>
-  <si>
-    <t>3A088A3D4FF477ABA840F15143AEA8BF</t>
-  </si>
-  <si>
-    <t>7A96E64864C750A6F88775320686599F</t>
-  </si>
-  <si>
-    <t>AC788FF8895D042B520E8B348EF6A417</t>
-  </si>
-  <si>
-    <t>559A64D4E9F44AC28FA1DEAE18A99B3B</t>
+    <t>B7F2F8A98EDE069FA6E5E9F8F693919D</t>
+  </si>
+  <si>
+    <t>FF4819BEA9DBC26E16707E94241D523C</t>
+  </si>
+  <si>
+    <t>F7CA3A5068D1ED5ED1E8F0E2645201DC</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 09 Tlaxco</t>
+  </si>
+  <si>
+    <t>DABD8BA4F1FE55D434F7A8FEAB48A257</t>
+  </si>
+  <si>
+    <t>6320A62EFFA993BB939B4733C717F42A</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril de 2023 al 30 de junio de 2023, en el Colegio de Bachilleres del Estado de Tlaxcala, de acuerdo a la norma que establece atribuciones responsabilidades y/o funciones, estos son nombrados y se rigen de acuerdo los articulos 16, 18 y 30 de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala y al articulo 21 fraccion VIII del Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala, con relación a los prestadores de servicios profesionales que formen parte de la estructura orgánica, este sujeto obligado no genero información respecto a este tema.</t>
+  </si>
+  <si>
+    <t>82ACD8DEE0FBB7F7F09A1CD340C08685</t>
+  </si>
+  <si>
+    <t>F335B215D90BB9BD5D4C65EA0CB5E703</t>
+  </si>
+  <si>
+    <t>5D5FB6C8656205787C0BFB504D2DB28C</t>
+  </si>
+  <si>
+    <t>2FD4B0E416B2B76AC444C27A160F4329</t>
+  </si>
+  <si>
+    <t>DD1E639316DA95405E457EFBE8D5E4C5</t>
+  </si>
+  <si>
+    <t>9C18007174873B7246096AB96658D5E4</t>
+  </si>
+  <si>
+    <t>0D20276E6B8FA5638BDB6A48906CE99E</t>
+  </si>
+  <si>
+    <t>50B122C9C9E1F21BC339D85786DF987D</t>
+  </si>
+  <si>
+    <t>54D00B65F5E6A52256D1481600FAEDD2</t>
+  </si>
+  <si>
+    <t>Jefa de Departamento</t>
+  </si>
+  <si>
+    <t>Jefa de Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>8266C402962C0BFF6584655C221AC086</t>
+  </si>
+  <si>
+    <t>BB8C502A0232383B1321654A7AD51FAF</t>
+  </si>
+  <si>
+    <t>8743385EB205A2D459F05FE1E6D88053</t>
+  </si>
+  <si>
+    <t>DC5E8FBBC4453F372FC9B9F815EED95A</t>
+  </si>
+  <si>
+    <t>60D527F2A2180F02B7336FB16722E46E</t>
+  </si>
+  <si>
+    <t>7E1EC04BB1FD1F9C1B86039578E807C3</t>
+  </si>
+  <si>
+    <t>Subdirectora de Área</t>
+  </si>
+  <si>
+    <t>144DBCF2972C0047477196B9B49F55E2</t>
+  </si>
+  <si>
+    <t>9E278F632F0FD9191B6006BC420A20DE</t>
+  </si>
+  <si>
+    <t>FDC45DC9A63A0AFBFA4247C4986F024D</t>
+  </si>
+  <si>
+    <t>163499FC5CE59A3616E4C904A637DFED</t>
+  </si>
+  <si>
+    <t>27D7C9484E2F63157FBA628D21EDFC4F</t>
+  </si>
+  <si>
+    <t>FFE5007763C121E2C11F2916C433D958</t>
+  </si>
+  <si>
+    <t>F73EA947E7BC79E4820F4C8D15E77C31</t>
+  </si>
+  <si>
+    <t>Subdirección del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>D5C3664149C5DC0D1764651E88F40856</t>
+  </si>
+  <si>
+    <t>764C68BA6D193274D26556A92D39352D</t>
+  </si>
+  <si>
+    <t>F5D2EE642FE18E2C2E9AF3E3529D5816</t>
+  </si>
+  <si>
+    <t>52B3F2F445FED89CE93E12DCE4468E75</t>
+  </si>
+  <si>
+    <t>0EAF2EA0688F0988B00D16494F0D2436</t>
+  </si>
+  <si>
+    <t>1DE81653A5C51004A67E324AC6728431</t>
+  </si>
+  <si>
+    <t>04BB17A65FB5C1929598D51FA8CC3A46</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>42230CF626466D13FA290E5FD2F669EC</t>
+  </si>
+  <si>
+    <t>A80401A9703075B1E265DDCAA3DF7C1A</t>
+  </si>
+  <si>
+    <t>622842A25590ADB4AEDFE57674E24A17</t>
+  </si>
+  <si>
+    <t>Departamento de Orientación Educativa y Servicio Social</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Orientación Educativca y Servicio Social</t>
+  </si>
+  <si>
+    <t>34DA960C78906F076DA84BA989D5588E</t>
+  </si>
+  <si>
+    <t>E2678AC906BD22EC375B6007F9632488</t>
+  </si>
+  <si>
+    <t>2AF5D0C3690D85F832E862223A84B1D9</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>675C24E5908BB1C6B8031098FE0E278B</t>
+  </si>
+  <si>
+    <t>58F479B28E0F7F97EA798F7E56FF180B</t>
+  </si>
+  <si>
+    <t>CA79A1C95797E5A98D36B00901D02716</t>
+  </si>
+  <si>
+    <t>817D46918304217807482115ECAB2CDE</t>
+  </si>
+  <si>
+    <t>2B88DD10F08748BB562324A0222041C8</t>
+  </si>
+  <si>
+    <t>4CA0ABB6152F45A8531DCD5909DC6C8A</t>
+  </si>
+  <si>
+    <t>ADAF88A2A4823E5FFA90F61F2FC34D3A</t>
+  </si>
+  <si>
+    <t>B83B688669FFFC1E80FD5DC2BEF0FD7E</t>
+  </si>
+  <si>
+    <t>9E0D3B7240356A238C6C20049034C566</t>
+  </si>
+  <si>
+    <t>A2EAB67C69E1F9707EC67C103CF37EDC</t>
+  </si>
+  <si>
+    <t>6348A1ABF4C5787AAB479254E9BDD7A1</t>
+  </si>
+  <si>
+    <t>97678431DB2A91CE8B24647A514F6C96</t>
+  </si>
+  <si>
+    <t>BF4CCC4D42B90EAA235306001AB5D857</t>
+  </si>
+  <si>
+    <t>2313E29EA8C33FE736850C8BC245D577</t>
+  </si>
+  <si>
+    <t>4B540507D0E73F23BA45D05BCA428330</t>
+  </si>
+  <si>
+    <t>9C6CAB0017FD645DDE6A56527D354636</t>
+  </si>
+  <si>
+    <t>C51EB8F9D861F0972D2F44E699ECD159</t>
   </si>
 </sst>
 </file>
@@ -1342,20 +1432,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="37" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="60.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="111.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="95" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="47.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -1563,3752 +1653,4102 @@
     </row>
     <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>244</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>246</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>162</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>249</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>223</v>
+        <v>62</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>52</v>
+        <v>249</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>45</v>
+        <v>244</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>53</v>
+        <v>254</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P19" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>223</v>
+        <v>65</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>45</v>
+        <v>244</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>45</v>
+        <v>244</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>215</v>
+        <v>105</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>45</v>
+        <v>244</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>246</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>59</v>
+        <v>272</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="I32" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>260</v>
+        <v>181</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>261</v>
+        <v>66</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>128</v>
+        <v>234</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>69</v>
+        <v>206</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>231</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>62</v>
+        <v>208</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>45</v>
+        <v>290</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>90</v>
+        <v>217</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>55</v>
+        <v>201</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>249</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="F52" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G53" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="I53" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>48</v>
+        <v>216</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>45</v>
+        <v>298</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>57</v>
+        <v>244</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>136</v>
+        <v>306</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>289</v>
+        <v>53</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>290</v>
+        <v>54</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>173</v>
+        <v>315</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>181</v>
+        <v>319</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>182</v>
+        <v>320</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>55</v>
+        <v>204</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>48</v>
+        <v>197</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>290</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>55</v>
+        <v>201</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>189</v>
+        <v>324</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>190</v>
+        <v>121</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>55</v>
+        <v>201</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>196</v>
+        <v>129</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>290</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>202</v>
+        <v>123</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>204</v>
+        <v>52</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>117</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>207</v>
+        <v>118</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I83" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N82" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="P82" s="2" t="s">
-        <v>231</v>
+      <c r="J83" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
